--- a/AAII_Financials/Quarterly/NFTN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NFTN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>NFTN</t>
   </si>
@@ -656,82 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>42855</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>42766</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -777,8 +785,14 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -824,8 +838,14 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -871,8 +891,14 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -890,8 +916,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -937,8 +965,14 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,8 +1018,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1022,17 +1062,23 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1078,8 +1124,14 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1094,8 +1146,10 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1141,8 +1195,14 @@
       <c r="Q17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1188,8 +1248,14 @@
       <c r="Q18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1207,8 +1273,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1254,8 +1322,14 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1268,11 +1342,11 @@
       <c r="F21" s="3">
         <v>0</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>4</v>
@@ -1301,8 +1375,14 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1348,8 +1428,14 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1395,8 +1481,14 @@
       <c r="Q23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1442,8 +1534,14 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1489,8 +1587,14 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1536,8 +1640,14 @@
       <c r="Q26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1583,8 +1693,14 @@
       <c r="Q27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1630,8 +1746,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1677,8 +1799,14 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1724,8 +1852,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1771,8 +1905,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1818,8 +1958,14 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1865,8 +2011,14 @@
       <c r="Q33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1912,8 +2064,14 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1959,60 +2117,72 @@
       <c r="Q35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>42855</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>42766</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2030,8 +2200,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2049,8 +2221,10 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2096,8 +2270,14 @@
       <c r="Q41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3">
+        <v>0</v>
+      </c>
+      <c r="S41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2143,8 +2323,14 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2190,8 +2376,14 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2237,8 +2429,14 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2284,8 +2482,14 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2331,8 +2535,14 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2378,8 +2588,14 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2425,8 +2641,14 @@
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2472,8 +2694,14 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2519,8 +2747,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2566,8 +2800,14 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2613,8 +2853,14 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2660,8 +2906,14 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -2707,8 +2959,14 @@
       <c r="Q54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3">
+        <v>0</v>
+      </c>
+      <c r="S54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2726,8 +2984,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2745,8 +3005,10 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2792,8 +3054,14 @@
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2830,17 +3098,23 @@
       <c r="N58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
+      <c r="O58" s="3">
+        <v>100</v>
+      </c>
+      <c r="P58" s="3">
+        <v>100</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2874,20 +3148,26 @@
       <c r="M59" s="3">
         <v>0</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
+      <c r="N59" s="3">
+        <v>0</v>
       </c>
       <c r="O59" s="3">
         <v>0</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
+      <c r="P59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2933,8 +3213,14 @@
       <c r="Q60" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>100</v>
+      </c>
+      <c r="S60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2980,8 +3266,14 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3027,8 +3319,14 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3074,8 +3372,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3121,8 +3425,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3168,8 +3478,14 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3215,8 +3531,14 @@
       <c r="Q66" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3">
+        <v>100</v>
+      </c>
+      <c r="S66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3234,8 +3556,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3281,8 +3605,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3328,8 +3658,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3375,8 +3711,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3422,8 +3764,14 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3449,10 +3797,10 @@
         <v>-200</v>
       </c>
       <c r="K72" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="L72" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="M72" s="3">
         <v>-100</v>
@@ -3469,8 +3817,14 @@
       <c r="Q72" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3516,8 +3870,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3563,8 +3923,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3610,8 +3976,14 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -3657,8 +4029,14 @@
       <c r="Q76" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S76" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3704,60 +4082,72 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>42855</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>42766</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3803,8 +4193,14 @@
       <c r="Q81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3822,8 +4218,10 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3869,8 +4267,14 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3916,8 +4320,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3963,8 +4373,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4010,8 +4426,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4057,8 +4479,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4104,8 +4532,14 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4151,8 +4585,14 @@
       <c r="Q89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4170,8 +4610,10 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4217,8 +4659,14 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4264,8 +4712,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4311,8 +4765,14 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4358,8 +4818,14 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4377,8 +4843,10 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4424,8 +4892,14 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4471,8 +4945,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4518,8 +4998,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4565,8 +5051,14 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4612,8 +5104,14 @@
       <c r="Q100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4659,8 +5157,14 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4704,6 +5208,12 @@
         <v>0</v>
       </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NFTN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NFTN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
   <si>
     <t>NFTN</t>
   </si>
@@ -656,90 +656,97 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44227</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>42855</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>42766</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -791,8 +798,14 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -844,8 +857,14 @@
       <c r="S9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -897,8 +916,14 @@
       <c r="S10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,8 +943,10 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -971,8 +998,14 @@
       <c r="S12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,8 +1057,14 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1068,17 +1107,23 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1130,8 +1175,14 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,8 +1199,10 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1201,8 +1254,14 @@
       <c r="S17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3">
+        <v>0</v>
+      </c>
+      <c r="U17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1254,8 +1313,14 @@
       <c r="S18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1275,8 +1340,10 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1328,8 +1395,14 @@
       <c r="S20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1348,11 +1421,11 @@
       <c r="H21" s="3">
         <v>0</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
@@ -1381,8 +1454,14 @@
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1434,13 +1513,19 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>0</v>
+      <c r="D23" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E23" s="3">
         <v>0</v>
@@ -1487,8 +1572,14 @@
       <c r="S23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1540,8 +1631,14 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,13 +1690,19 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>0</v>
+      <c r="D26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E26" s="3">
         <v>0</v>
@@ -1646,13 +1749,19 @@
       <c r="S26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>0</v>
+      <c r="D27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E27" s="3">
         <v>0</v>
@@ -1699,8 +1808,14 @@
       <c r="S27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1867,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1805,8 +1926,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1985,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,8 +2044,14 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1964,13 +2103,19 @@
       <c r="S32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>0</v>
+      <c r="D33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E33" s="3">
         <v>0</v>
@@ -2017,8 +2162,14 @@
       <c r="S33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,13 +2221,19 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>0</v>
+      <c r="D35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E35" s="3">
         <v>0</v>
@@ -2123,66 +2280,78 @@
       <c r="S35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44227</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>42855</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>42766</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2371,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,8 +2394,10 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2276,8 +2449,14 @@
       <c r="S41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2329,8 +2508,14 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2382,8 +2567,14 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2435,8 +2626,14 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2488,8 +2685,14 @@
       <c r="S45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2541,8 +2744,14 @@
       <c r="S46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2594,8 +2803,14 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2647,8 +2862,14 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2700,8 +2921,14 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2980,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,8 +3039,14 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2859,8 +3098,14 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,8 +3157,14 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -2965,8 +3216,14 @@
       <c r="S54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3">
+        <v>0</v>
+      </c>
+      <c r="U54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3243,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,8 +3266,10 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3060,8 +3321,14 @@
       <c r="S57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3104,17 +3371,23 @@
       <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>4</v>
+      <c r="Q58" s="3">
+        <v>100</v>
+      </c>
+      <c r="R58" s="3">
+        <v>100</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3154,28 +3427,34 @@
       <c r="O59" s="3">
         <v>0</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
+      <c r="P59" s="3">
+        <v>0</v>
       </c>
       <c r="Q59" s="3">
         <v>0</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
+      <c r="R59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3">
+        <v>0</v>
+      </c>
+      <c r="U59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F60" s="3">
         <v>100</v>
@@ -3219,8 +3498,14 @@
       <c r="S60" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3">
+        <v>100</v>
+      </c>
+      <c r="U60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3272,8 +3557,14 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3325,8 +3616,14 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3675,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3734,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,16 +3793,22 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>100</v>
+      <c r="D66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E66" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F66" s="3">
         <v>100</v>
@@ -3537,8 +3852,14 @@
       <c r="S66" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3">
+        <v>100</v>
+      </c>
+      <c r="U66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3879,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3934,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3993,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3717,8 +4052,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,8 +4111,14 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3803,10 +4150,10 @@
         <v>-200</v>
       </c>
       <c r="M72" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="N72" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="O72" s="3">
         <v>-100</v>
@@ -3823,8 +4170,14 @@
       <c r="S72" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4229,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4288,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,16 +4347,22 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="E76" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="F76" s="3">
         <v>-100</v>
@@ -4035,8 +4406,14 @@
       <c r="S76" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U76" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,71 +4465,83 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44227</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>42855</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>42766</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>0</v>
+      <c r="D81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E81" s="3">
         <v>0</v>
@@ -4199,8 +4588,14 @@
       <c r="S81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,8 +4615,10 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4273,8 +4670,14 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4729,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4788,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4847,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4906,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,8 +4965,14 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4591,8 +5024,14 @@
       <c r="S89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,8 +5051,10 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4665,8 +5106,14 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +5165,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,8 +5224,14 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4824,8 +5283,14 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,8 +5310,10 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4898,8 +5365,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5424,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5483,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,8 +5542,14 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5110,8 +5601,14 @@
       <c r="S100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5163,8 +5660,14 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5214,6 +5717,12 @@
         <v>0</v>
       </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>0</v>
       </c>
     </row>
